--- a/data/trans_dic/P15D$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,71; 75,63</t>
+          <t>15,36; 70,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,45; 52,33</t>
+          <t>17,37; 50,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 35,66</t>
+          <t>3,34; 36,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 46,93</t>
+          <t>11,04; 49,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,28</t>
+          <t>0,0; 43,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,01</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 35,77</t>
+          <t>9,54; 35,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,04; 55,38</t>
+          <t>13,72; 54,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 38,95</t>
+          <t>12,5; 38,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 19,01</t>
+          <t>1,85; 18,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,07; 36,69</t>
+          <t>13,81; 37,72</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 60,79</t>
+          <t>11,56; 60,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 45,27</t>
+          <t>11,97; 45,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,48</t>
+          <t>0,0; 29,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 56,03</t>
+          <t>8,32; 53,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 96,83</t>
+          <t>0,0; 87,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 47,08</t>
+          <t>9,88; 45,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 41,93</t>
+          <t>4,6; 42,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 28,69</t>
+          <t>6,1; 30,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,4; 62,86</t>
+          <t>17,26; 62,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,33; 40,4</t>
+          <t>15,02; 38,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 28,58</t>
+          <t>2,96; 29,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 41,57</t>
+          <t>10,79; 37,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 40,92</t>
+          <t>6,46; 39,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 32,63</t>
+          <t>11,0; 32,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 36,47</t>
+          <t>6,24; 33,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 20,48</t>
+          <t>2,86; 21,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,13; 100,0</t>
+          <t>15,61; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,18</t>
+          <t>0,0; 39,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,66</t>
+          <t>0,0; 63,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 41,29</t>
+          <t>4,87; 41,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 43,61</t>
+          <t>12,18; 43,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 30,33</t>
+          <t>10,97; 29,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 34,07</t>
+          <t>7,98; 33,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 21,62</t>
+          <t>5,66; 22,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 36,46</t>
+          <t>9,68; 35,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 39,34</t>
+          <t>21,4; 39,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 18,61</t>
+          <t>3,09; 18,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 30,72</t>
+          <t>11,45; 30,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,6</t>
+          <t>0,0; 22,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 38,29</t>
+          <t>12,3; 37,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 37,88</t>
+          <t>10,41; 35,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 20,18</t>
+          <t>6,14; 20,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 25,68</t>
+          <t>8,22; 27,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,94; 35,32</t>
+          <t>20,24; 34,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 22,25</t>
+          <t>7,84; 21,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 23,8</t>
+          <t>10,27; 23,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,47</t>
+          <t>0,0; 45,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 28,55</t>
+          <t>5,18; 29,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 39,34</t>
+          <t>12,87; 40,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 25,55</t>
+          <t>4,58; 26,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 36,28</t>
+          <t>3,79; 31,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,83; 41,46</t>
+          <t>16,61; 40,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 31,14</t>
+          <t>4,43; 27,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 26,44</t>
+          <t>10,2; 25,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 28,87</t>
+          <t>4,91; 28,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,55; 32,56</t>
+          <t>14,24; 31,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 29,44</t>
+          <t>11,4; 29,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 21,23</t>
+          <t>8,97; 22,05</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,73; 65,78</t>
+          <t>16,18; 63,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 38,95</t>
+          <t>7,38; 38,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,35; 46,47</t>
+          <t>11,83; 47,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,13</t>
+          <t>0,0; 44,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,3; 34,17</t>
+          <t>6,5; 33,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,4; 50,01</t>
+          <t>29,24; 49,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 22,39</t>
+          <t>5,15; 24,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,19; 41,56</t>
+          <t>18,24; 42,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,99; 38,4</t>
+          <t>13,04; 38,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,7; 44,41</t>
+          <t>25,77; 43,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,13; 27,91</t>
+          <t>10,31; 26,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 36,34</t>
+          <t>14,05; 35,81</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,28; 34,61</t>
+          <t>18,69; 35,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,5; 30,95</t>
+          <t>19,99; 30,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,06; 22,02</t>
+          <t>11,44; 22,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 22,91</t>
+          <t>11,75; 23,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,23; 24,85</t>
+          <t>9,93; 25,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,3; 34,01</t>
+          <t>22,37; 34,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,55</t>
+          <t>9,48; 20,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 23,98</t>
+          <t>14,37; 23,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 28,42</t>
+          <t>16,22; 27,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,95</t>
+          <t>22,83; 30,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,28</t>
+          <t>11,93; 19,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,4; 21,52</t>
+          <t>13,9; 21,52</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1853; 9528</t>
+          <t>1935; 8859</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5928; 17773</t>
+          <t>5900; 17291</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>787; 7680</t>
+          <t>719; 7829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2177; 11186</t>
+          <t>2632; 11870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4446</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>0; 4409</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2233; 8302</t>
+          <t>2215; 8241</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2655; 11274</t>
+          <t>2793; 11097</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6762; 19976</t>
+          <t>6413; 19647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>783; 7910</t>
+          <t>769; 7841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6151; 17260</t>
+          <t>6499; 17744</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1667; 8074</t>
+          <t>1535; 8038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3973; 14689</t>
+          <t>3885; 14694</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5139</t>
+          <t>0; 5023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2165; 13530</t>
+          <t>2010; 12816</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5411</t>
+          <t>0; 4869</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2362; 12643</t>
+          <t>2654; 12162</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>997; 9262</t>
+          <t>1016; 9473</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1187; 6645</t>
+          <t>1413; 7006</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3095; 11861</t>
+          <t>3256; 11729</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9681; 23958</t>
+          <t>8907; 22923</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1129; 11130</t>
+          <t>1152; 11662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5221; 19666</t>
+          <t>5105; 17800</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2091; 11574</t>
+          <t>1826; 11066</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6420; 18479</t>
+          <t>6230; 18351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2021; 11330</t>
+          <t>1940; 10284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1016; 6828</t>
+          <t>955; 7192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>799; 4957</t>
+          <t>774; 4957</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5905</t>
+          <t>0; 5595</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5601</t>
+          <t>0; 5578</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>605; 4955</t>
+          <t>584; 4923</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4166; 14498</t>
+          <t>4050; 14366</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8116; 21423</t>
+          <t>7747; 20518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3225; 13580</t>
+          <t>3180; 13324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2283; 9804</t>
+          <t>2564; 10056</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4152; 14227</t>
+          <t>3777; 13921</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20720; 37613</t>
+          <t>20459; 38147</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1963; 10977</t>
+          <t>1824; 11038</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7030; 20427</t>
+          <t>7612; 20584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5902</t>
+          <t>0; 5639</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6246; 18641</t>
+          <t>5989; 18216</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4018; 14572</t>
+          <t>4003; 13722</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3053; 9992</t>
+          <t>3040; 10083</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5183; 16446</t>
+          <t>5264; 17806</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30211; 50971</t>
+          <t>29212; 50389</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7278; 21686</t>
+          <t>7643; 20505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12538; 27602</t>
+          <t>11908; 27023</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5747</t>
+          <t>0; 5699</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2038; 10927</t>
+          <t>1984; 11425</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5106; 16357</t>
+          <t>5352; 16632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1956; 9786</t>
+          <t>1754; 10322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>896; 8144</t>
+          <t>852; 7160</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10380; 24141</t>
+          <t>9672; 23656</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2088; 12586</t>
+          <t>1789; 11172</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5187; 14045</t>
+          <t>5421; 13667</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1804; 10131</t>
+          <t>1721; 9891</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15009; 31419</t>
+          <t>13746; 30806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9149; 24138</t>
+          <t>9349; 24573</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7969; 19415</t>
+          <t>8202; 20163</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2870; 10650</t>
+          <t>2620; 10256</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2518; 10448</t>
+          <t>1981; 10454</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3359; 13753</t>
+          <t>3500; 14095</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5762</t>
+          <t>0; 5251</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1767; 9581</t>
+          <t>1823; 9446</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25352; 44637</t>
+          <t>26102; 44385</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3056; 13529</t>
+          <t>3110; 14954</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8486; 19382</t>
+          <t>8508; 19835</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5748; 16988</t>
+          <t>5768; 17156</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30988; 51552</t>
+          <t>29917; 50399</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9118; 25132</t>
+          <t>9286; 23797</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8277; 21212</t>
+          <t>8204; 20901</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22308; 42233</t>
+          <t>22806; 42751</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58173; 87817</t>
+          <t>56722; 87176</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22072; 43968</t>
+          <t>22845; 44501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22981; 45330</t>
+          <t>23248; 46886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9594; 23310</t>
+          <t>9318; 23607</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56707; 86513</t>
+          <t>56893; 87597</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17651; 39101</t>
+          <t>18046; 38099</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30045; 49800</t>
+          <t>29843; 47962</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36237; 61331</t>
+          <t>35008; 59768</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>124316; 166554</t>
+          <t>122858; 162758</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46506; 75176</t>
+          <t>46519; 74381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>58380; 87278</t>
+          <t>56347; 87247</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 70,32</t>
+          <t>15,57; 74,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 50,91</t>
+          <t>15,47; 51,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 36,35</t>
+          <t>0,0; 34,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 49,8</t>
+          <t>9,76; 46,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,37</t>
+          <t>0,0; 56,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,44</t>
+          <t>0,0; 28,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 35,51</t>
+          <t>10,64; 34,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,72; 54,51</t>
+          <t>12,67; 57,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 38,3</t>
+          <t>12,04; 38,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 18,85</t>
+          <t>1,85; 19,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 37,72</t>
+          <t>12,39; 33,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 60,52</t>
+          <t>12,79; 62,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 45,29</t>
+          <t>11,89; 44,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,79</t>
+          <t>0,0; 24,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 53,07</t>
+          <t>7,79; 48,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,13</t>
+          <t>0,0; 84,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 45,29</t>
+          <t>10,55; 46,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 42,89</t>
+          <t>4,37; 41,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 30,25</t>
+          <t>6,61; 29,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 62,17</t>
+          <t>17,14; 63,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 38,66</t>
+          <t>15,65; 40,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 29,94</t>
+          <t>2,89; 27,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 37,63</t>
+          <t>10,17; 35,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 39,12</t>
+          <t>7,27; 40,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 32,4</t>
+          <t>11,57; 33,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 33,1</t>
+          <t>6,29; 32,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 21,57</t>
+          <t>3,6; 22,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 100,0</t>
+          <t>16,13; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,97</t>
+          <t>0,0; 41,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,4</t>
+          <t>0,0; 63,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 41,03</t>
+          <t>4,79; 40,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 43,22</t>
+          <t>12,57; 44,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,97; 29,05</t>
+          <t>11,37; 29,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,98; 33,42</t>
+          <t>7,56; 33,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,18</t>
+          <t>5,97; 21,16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 35,68</t>
+          <t>9,99; 35,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,4; 39,89</t>
+          <t>21,41; 40,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 18,71</t>
+          <t>3,01; 17,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 30,96</t>
+          <t>9,48; 27,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,55</t>
+          <t>0,0; 26,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 37,42</t>
+          <t>12,52; 38,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 35,67</t>
+          <t>9,95; 37,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 20,37</t>
+          <t>6,23; 19,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 27,81</t>
+          <t>8,79; 26,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 34,92</t>
+          <t>19,99; 35,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 21,04</t>
+          <t>8,14; 22,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 23,3</t>
+          <t>9,84; 21,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,08</t>
+          <t>0,0; 49,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 29,85</t>
+          <t>5,23; 30,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,87; 40,0</t>
+          <t>13,04; 39,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 26,95</t>
+          <t>4,04; 22,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 31,9</t>
+          <t>3,84; 34,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61; 40,63</t>
+          <t>16,3; 40,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 27,65</t>
+          <t>5,22; 27,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 25,73</t>
+          <t>9,18; 24,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 28,19</t>
+          <t>5,02; 28,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 31,92</t>
+          <t>15,66; 32,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 29,97</t>
+          <t>11,04; 29,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 22,05</t>
+          <t>8,79; 20,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,18; 63,34</t>
+          <t>15,9; 63,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 38,97</t>
+          <t>7,43; 39,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,83; 47,63</t>
+          <t>12,72; 48,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,77</t>
+          <t>0,0; 44,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 33,69</t>
+          <t>6,46; 34,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,24; 49,73</t>
+          <t>29,88; 50,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 24,74</t>
+          <t>5,17; 22,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,24; 42,53</t>
+          <t>15,5; 38,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 38,78</t>
+          <t>12,78; 39,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,77; 43,42</t>
+          <t>26,58; 43,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,31; 26,43</t>
+          <t>10,32; 27,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,05; 35,81</t>
+          <t>13,5; 34,47</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,69; 35,04</t>
+          <t>18,92; 35,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,99; 30,72</t>
+          <t>19,97; 30,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 22,29</t>
+          <t>11,67; 22,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 23,7</t>
+          <t>10,99; 20,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,17</t>
+          <t>10,6; 25,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,44</t>
+          <t>22,94; 34,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,02</t>
+          <t>9,54; 19,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 23,1</t>
+          <t>13,54; 21,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,22; 27,69</t>
+          <t>16,72; 27,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,25</t>
+          <t>22,87; 30,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,08</t>
+          <t>11,7; 19,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,9; 21,52</t>
+          <t>13,27; 19,92</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10848</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1935; 8859</t>
+          <t>1961; 9437</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5900; 17291</t>
+          <t>5254; 17652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>719; 7829</t>
+          <t>0; 7522</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2632; 11870</t>
+          <t>2526; 12002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3366</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>0; 4926</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2215; 8241</t>
+          <t>2787; 9137</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2793; 11097</t>
+          <t>2580; 11650</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6413; 19647</t>
+          <t>6177; 19761</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>769; 7841</t>
+          <t>768; 8015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6499; 17744</t>
+          <t>6449; 17435</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9443</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1535; 8038</t>
+          <t>1699; 8259</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3885; 14694</t>
+          <t>3858; 14557</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5023</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2010; 12816</t>
+          <t>2005; 12537</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 4748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2654; 12162</t>
+          <t>2833; 12447</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1016; 9473</t>
+          <t>965; 9131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1413; 7006</t>
+          <t>1653; 7423</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3256; 11729</t>
+          <t>3233; 11935</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8907; 22923</t>
+          <t>9282; 24009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1152; 11662</t>
+          <t>1125; 10883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5105; 17800</t>
+          <t>5159; 18147</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>6143</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1826; 11066</t>
+          <t>2057; 11432</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6230; 18351</t>
+          <t>6551; 19222</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1940; 10284</t>
+          <t>1954; 10138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>955; 7192</t>
+          <t>1343; 8298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>774; 4957</t>
+          <t>799; 4957</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5595</t>
+          <t>0; 5743</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5578</t>
+          <t>0; 5559</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>584; 4923</t>
+          <t>608; 5155</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4050; 14366</t>
+          <t>4179; 14855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7747; 20518</t>
+          <t>8032; 20743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3180; 13324</t>
+          <t>3013; 13427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2564; 10056</t>
+          <t>2981; 10570</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>19383</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3777; 13921</t>
+          <t>3899; 13752</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20459; 38147</t>
+          <t>20468; 38813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1824; 11038</t>
+          <t>1777; 10466</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7612; 20584</t>
+          <t>7374; 21041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5639</t>
+          <t>0; 6631</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5989; 18216</t>
+          <t>6095; 18615</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4003; 13722</t>
+          <t>3828; 14442</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3040; 10083</t>
+          <t>3453; 11067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5264; 17806</t>
+          <t>5629; 16798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29212; 50389</t>
+          <t>28843; 51566</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7643; 20505</t>
+          <t>7928; 21657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11908; 27023</t>
+          <t>13106; 28934</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13208</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5699</t>
+          <t>0; 6227</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1984; 11425</t>
+          <t>2004; 11543</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5352; 16632</t>
+          <t>5421; 16343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1754; 10322</t>
+          <t>1628; 8901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>852; 7160</t>
+          <t>863; 7793</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9672; 23656</t>
+          <t>9492; 23500</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1789; 11172</t>
+          <t>2108; 11161</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5421; 13667</t>
+          <t>5229; 14078</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1721; 9891</t>
+          <t>1761; 10168</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13746; 30806</t>
+          <t>15117; 30973</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9349; 24573</t>
+          <t>9052; 24173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8202; 20163</t>
+          <t>8551; 19931</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13573</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2620; 10256</t>
+          <t>2575; 10255</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1981; 10454</t>
+          <t>1992; 10670</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3500; 14095</t>
+          <t>3765; 14369</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5251</t>
+          <t>0; 5002</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1823; 9446</t>
+          <t>1811; 9642</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26102; 44385</t>
+          <t>26666; 45028</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3110; 14954</t>
+          <t>3124; 13889</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8508; 19835</t>
+          <t>7628; 18980</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5768; 17156</t>
+          <t>5653; 17324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29917; 50399</t>
+          <t>30848; 51046</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9286; 23797</t>
+          <t>9293; 25134</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8204; 20901</t>
+          <t>8159; 20828</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>33202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>72598</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22806; 42751</t>
+          <t>23087; 43144</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56722; 87176</t>
+          <t>56671; 86248</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22845; 44501</t>
+          <t>23303; 44783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23248; 46886</t>
+          <t>23980; 45045</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9318; 23607</t>
+          <t>9943; 24120</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56893; 87597</t>
+          <t>58345; 87992</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18046; 38099</t>
+          <t>18150; 37960</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29843; 47962</t>
+          <t>30512; 49144</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35008; 59768</t>
+          <t>36095; 60051</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122858; 162758</t>
+          <t>123051; 165548</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46519; 74381</t>
+          <t>45605; 74175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56347; 87247</t>
+          <t>58870; 88364</t>
         </is>
       </c>
     </row>
